--- a/artfynd/A 26606-2025 artfynd.xlsx
+++ b/artfynd/A 26606-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119333234</v>
+        <v>119333328</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527436</v>
+        <v>527404</v>
       </c>
       <c r="R2" t="n">
-        <v>6868268</v>
+        <v>6868503</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -792,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119333301</v>
+        <v>119332979</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +798,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>3100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Laforsenområdet, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527434</v>
+        <v>527433</v>
       </c>
       <c r="R3" t="n">
-        <v>6868348</v>
+        <v>6868305</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119332979</v>
+        <v>119332983</v>
       </c>
       <c r="B4" t="n">
-        <v>91826</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,12 +913,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527433</v>
+        <v>527534</v>
       </c>
       <c r="R4" t="n">
-        <v>6868305</v>
+        <v>6868409</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,6 +981,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,15 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119332934</v>
+        <v>119333352</v>
       </c>
       <c r="B5" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,34 +1011,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Laforsenområdet, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527401</v>
+        <v>527640</v>
       </c>
       <c r="R5" t="n">
-        <v>6868445</v>
+        <v>6868662</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1075,12 +1074,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,21 +1090,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1122,59 +1106,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119332983</v>
+        <v>119333234</v>
       </c>
       <c r="B6" t="n">
-        <v>91826</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3100</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Laforsenområdet, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527534</v>
+        <v>527436</v>
       </c>
       <c r="R6" t="n">
-        <v>6868409</v>
+        <v>6868268</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1201,12 +1171,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,9 +1185,23 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1231,6 +1215,521 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119333235</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Laforsenområdet, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>527407</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6868466</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119333254</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Laforsenområdet, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>527480</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6868644</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>119333262</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Laforsenområdet, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>527643</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6868386</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119333301</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Laforsenområdet, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>527434</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6868348</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>119332934</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Laforsenområdet, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>527401</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6868445</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26606-2025 artfynd.xlsx
+++ b/artfynd/A 26606-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119333328</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119332979</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119332983</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119333352</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119333234</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119333235</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119333254</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1521,6 +1561,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119333262</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1618,6 +1663,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119333301</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1730,8 +1780,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119332934</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>